--- a/app/templates_excel/citrinitas/c1_en.xlsx
+++ b/app/templates_excel/citrinitas/c1_en.xlsx
@@ -267,10 +267,6 @@
     <t>Taurus 5</t>
   </si>
   <si>
-    <t>A window at an open grave.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Taurus 6</t>
   </si>
   <si>
@@ -728,10 +724,6 @@
     <t>Cancer 12</t>
   </si>
   <si>
-    <t>Chinese woman nusing a baby with a message.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Cancer 13</t>
   </si>
   <si>
@@ -955,10 +947,6 @@
     <t>Leo 15</t>
   </si>
   <si>
-    <t>A pagent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Leo 16</t>
   </si>
   <si>
@@ -2298,10 +2286,6 @@
     <t>Aquarius 28</t>
   </si>
   <si>
-    <t>A tree feiled and sawed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Aquarius 29</t>
   </si>
   <si>
@@ -2438,10 +2422,6 @@
     <t>Pisces 18</t>
   </si>
   <si>
-    <t>A gigatic tent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Pisces 19</t>
   </si>
   <si>
@@ -2480,10 +2460,6 @@
     <t>Pisces 24</t>
   </si>
   <si>
-    <t>An inhibited island.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Pisces 25</t>
   </si>
   <si>
@@ -2567,6 +2543,30 @@
   </si>
   <si>
     <t>Rock formations at the edge of a precipice.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A gigantic tent.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tree felled and sawed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese woman nursing a baby with a message.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A widow at an open grave.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A pageant.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An inhabited island.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="4" spans="1:54" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
     </row>
     <row r="5" spans="1:54" ht="15" x14ac:dyDescent="0.3">
@@ -3160,10 +3160,10 @@
       <c r="AY8" s="4"/>
       <c r="AZ8" s="4"/>
       <c r="BA8" s="4" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="BB8" s="4" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
     </row>
     <row r="9" spans="1:54" ht="15" x14ac:dyDescent="0.3">
@@ -3286,7 +3286,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:53" ht="15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A24" s="5" t="s">
         <v>33</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:53" ht="15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A25" s="5" t="s">
         <v>35</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:53" ht="15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:53" ht="15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:53" ht="15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A28" s="5" t="s">
         <v>41</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="1:53" ht="15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A29" s="5" t="s">
         <v>43</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:53" ht="15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A30" s="5" t="s">
         <v>45</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:53" ht="15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A31" s="5" t="s">
         <v>47</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:53" ht="15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A32" s="5" t="s">
         <v>49</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:54" ht="15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A33" s="5" t="s">
         <v>51</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:54" ht="15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A34" s="5" t="s">
         <v>53</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:54" ht="15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A35" s="5" t="s">
         <v>55</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:54" ht="15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A36" s="5" t="s">
         <v>57</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:54" ht="15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
         <v>59</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:54" ht="15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A38" s="5" t="s">
         <v>61</v>
       </c>
@@ -3406,168 +3406,168 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA39" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB39" s="7" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="40" spans="1:54" ht="15" x14ac:dyDescent="0.3">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="40" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A40" s="8" t="s">
         <v>63</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:54" ht="15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A41" s="8" t="s">
         <v>65</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:54" ht="15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A42" s="8" t="s">
         <v>67</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="43" spans="1:54" ht="15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A43" s="8" t="s">
         <v>69</v>
       </c>
@@ -3599,4386 +3599,4386 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:54" ht="15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A44" s="8" t="s">
         <v>71</v>
       </c>
       <c r="BA44" s="6" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="45" spans="1:54" x14ac:dyDescent="0.4">
+      <c r="A45" s="8" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="45" spans="1:54" ht="15" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="BA45" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="BA45" s="6" t="s">
+    </row>
+    <row r="46" spans="1:54" x14ac:dyDescent="0.4">
+      <c r="A46" s="8" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="46" spans="1:54" ht="15" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
+      <c r="BA46" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="BA46" s="6" t="s">
+    </row>
+    <row r="47" spans="1:54" x14ac:dyDescent="0.4">
+      <c r="A47" s="8" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="47" spans="1:54" ht="15" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+      <c r="BA47" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="BA47" s="6" t="s">
+    </row>
+    <row r="48" spans="1:54" x14ac:dyDescent="0.4">
+      <c r="A48" s="8" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="48" spans="1:54" ht="15" x14ac:dyDescent="0.3">
-      <c r="A48" s="8" t="s">
+      <c r="BA48" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="BA48" s="6" t="s">
+    </row>
+    <row r="49" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A49" s="8" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="49" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
+      <c r="BA49" s="6" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="50" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A50" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="BA49" s="6" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="50" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A50" s="8" t="s">
+      <c r="BA50" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="BA50" s="6" t="s">
+    </row>
+    <row r="51" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A51" s="8" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="51" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A51" s="8" t="s">
+      <c r="BA51" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="BA51" s="6" t="s">
+    </row>
+    <row r="52" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A52" s="8" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="52" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
+      <c r="BA52" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="BA52" s="6" t="s">
+    </row>
+    <row r="53" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A53" s="8" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="53" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A53" s="8" t="s">
+      <c r="BA53" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="BA53" s="6" t="s">
+    </row>
+    <row r="54" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A54" s="8" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="54" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A54" s="8" t="s">
+      <c r="BA54" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="BA54" s="6" t="s">
+    </row>
+    <row r="55" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A55" s="8" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="55" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A55" s="8" t="s">
+      <c r="BA55" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="BA55" s="6" t="s">
+    </row>
+    <row r="56" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A56" s="8" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="56" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A56" s="8" t="s">
+      <c r="BA56" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="BA56" s="6" t="s">
+    </row>
+    <row r="57" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A57" s="8" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="57" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A57" s="8" t="s">
+      <c r="BA57" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="BA57" s="6" t="s">
+    </row>
+    <row r="58" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A58" s="8" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="58" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A58" s="8" t="s">
+      <c r="BA58" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="BA58" s="6" t="s">
+    </row>
+    <row r="59" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A59" s="8" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="59" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A59" s="8" t="s">
+      <c r="BA59" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="BA59" s="6" t="s">
+    </row>
+    <row r="60" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A60" s="8" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="60" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A60" s="8" t="s">
+      <c r="BA60" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="BA60" s="6" t="s">
+    </row>
+    <row r="61" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A61" s="8" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="61" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A61" s="8" t="s">
+      <c r="BA61" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="BA61" s="6" t="s">
+    </row>
+    <row r="62" spans="1:53" x14ac:dyDescent="0.4">
+      <c r="A62" s="8" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="62" spans="1:53" ht="15" x14ac:dyDescent="0.3">
-      <c r="A62" s="8" t="s">
+      <c r="BA62" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="BA62" s="6" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A63" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="BA63" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="BA63" s="6" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="64" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A64" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="BA64" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="BA64" s="6" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A65" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="BA65" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="BA65" s="6" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A66" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA66" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="BA66" s="6" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A67" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="BA67" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="BA67" s="6" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="68" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A68" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="BA68" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="BA68" s="6" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A69" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="BA69" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="BA69" s="6" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B70" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA70" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB70" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="71" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A71" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BA71" s="6" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
     </row>
     <row r="72" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A72" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="BA72" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="BA72" s="6" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A73" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="BA73" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="BA73" s="6" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A74" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="BA74" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="BA74" s="6" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="75" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A75" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="BA75" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="BA75" s="6" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="76" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A76" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA76" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="BA76" s="6" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="77" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A77" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA77" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="BA77" s="6" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="78" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A78" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="BA78" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="BA78" s="6" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A79" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="BA79" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="BA79" s="6" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="80" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A80" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="BA80" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="BA80" s="6" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="81" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A81" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA81" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="BA81" s="6" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="82" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A82" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="BA82" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="BA82" s="6" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="83" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A83" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="BA83" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="BA83" s="6" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A84" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="BA84" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="BA84" s="6" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="85" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A85" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="BA85" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="BA85" s="6" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="86" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A86" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="BA86" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="BA86" s="6" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="87" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A87" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="BA87" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="BA87" s="6" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="88" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A88" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="BA88" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="BA88" s="6" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A89" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="BA89" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="BA89" s="6" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="90" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A90" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="BA90" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="BA90" s="6" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="91" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A91" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA91" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="BA91" s="6" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="92" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A92" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="BA92" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="BA92" s="6" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="93" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A93" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="BA93" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="BA93" s="6" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="94" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A94" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="BA94" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="BA94" s="6" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="95" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A95" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="BA95" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="BA95" s="6" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="96" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A96" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="BA96" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="BA96" s="6" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="97" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A97" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="BA97" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="BA97" s="6" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="98" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A98" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA98" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="BA98" s="6" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="99" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A99" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="BA99" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="BA99" s="6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="100" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A100" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="BA100" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="BA100" s="6" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B101" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA101" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB101" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="102" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A102" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="BA102" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="BA102" s="6" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="103" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A103" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="BA103" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="BA103" s="6" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A104" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="BA104" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="BA104" s="6" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="105" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A105" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="BA105" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="BA105" s="6" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="106" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A106" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="BA106" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="BA106" s="6" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="107" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A107" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="BA107" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="BA107" s="6" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="108" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A108" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="BA108" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="BA108" s="6" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A109" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="BA109" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="BA109" s="6" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="110" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A110" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="BA110" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="BA110" s="6" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="111" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A111" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="BA111" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="BA111" s="6" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="112" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A112" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="BA112" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="BA112" s="6" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="113" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A113" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BA113" s="6" t="s">
-        <v>204</v>
+        <v>725</v>
       </c>
     </row>
     <row r="114" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A114" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="BA114" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A115" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="BA115" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="116" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A116" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="BA116" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="117" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A117" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="BA117" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="118" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A118" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="BA118" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="119" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A119" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="BA119" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="120" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A120" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="BA120" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="121" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A121" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="BA121" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="122" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A122" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="BA122" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="123" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A123" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="BA123" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="124" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A124" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="BA124" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="125" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A125" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="BA125" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="126" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A126" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="BA126" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="127" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A127" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="BA127" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="128" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A128" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="BA128" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="129" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A129" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="BA129" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="130" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A130" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="BA130" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="131" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A131" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="BA131" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="132" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA132" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB132" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="133" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A133" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="BA133" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="134" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A134" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="BA134" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="135" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A135" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="BA135" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="136" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A136" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="BA136" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="137" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A137" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="BA137" s="6" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="138" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A138" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="BA138" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="139" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A139" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="BA139" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="140" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A140" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="BA140" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="141" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A141" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="BA141" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="142" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A142" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="BA142" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="143" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A143" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="BA143" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="144" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A144" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="BA144" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="145" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A145" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="BA145" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="146" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A146" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="BA146" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="147" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A147" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="BA147" s="6" t="s">
-        <v>269</v>
+        <v>727</v>
       </c>
     </row>
     <row r="148" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A148" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="BA148" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="149" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A149" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="BA149" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="150" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A150" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="BA150" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A151" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="BA151" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="152" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A152" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="BA152" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="153" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A153" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="BA153" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="154" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A154" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="BA154" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="155" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A155" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="BA155" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="156" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A156" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="BA156" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="157" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A157" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="BA157" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="158" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A158" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="BA158" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="159" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A159" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="BA159" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="160" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A160" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="BA160" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="161" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A161" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="BA161" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="162" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A162" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="BA162" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="163" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B163" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA163" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB163" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="164" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A164" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="BA164" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="165" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A165" s="8" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="BA165" s="6" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="166" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A166" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="BA166" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="167" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A167" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="BA167" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="168" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A168" s="8" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="BA168" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="169" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A169" s="8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="BA169" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="170" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A170" s="8" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="BA170" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="171" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A171" s="8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="BA171" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="172" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A172" s="8" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="BA172" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="173" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A173" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="BA173" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="174" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A174" s="8" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="BA174" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="175" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A175" s="8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="BA175" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="176" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A176" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="BA176" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="177" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A177" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="BA177" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="178" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A178" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="BA178" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="179" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A179" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="BA179" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="180" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A180" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="BA180" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="181" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A181" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="BA181" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="182" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A182" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="BA182" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="183" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A183" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="BA183" s="6" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="184" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A184" s="8" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="BA184" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="185" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A185" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="BA185" s="6" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="186" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A186" s="8" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="BA186" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="187" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A187" s="8" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="BA187" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="188" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A188" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="BA188" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="189" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A189" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="BA189" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="190" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A190" s="8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="BA190" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="191" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A191" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="BA191" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="192" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A192" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="BA192" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="193" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A193" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="BA193" s="6" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="194" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B194" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA194" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB194" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="195" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A195" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="BA195" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="196" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A196" s="9" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="BA196" s="6" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="197" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A197" s="9" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="BA197" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="198" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A198" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="BA198" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="199" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A199" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="BA199" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="200" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A200" s="9" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="BA200" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="201" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A201" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="BA201" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="202" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A202" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="BA202" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="203" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A203" s="9" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="BA203" s="6" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="204" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A204" s="9" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="BA204" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="205" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A205" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="BA205" s="6" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
     </row>
     <row r="206" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A206" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="BA206" s="6" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="207" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A207" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="BA207" s="6" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="208" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A208" s="9" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="BA208" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="209" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A209" s="9" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="BA209" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="210" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A210" s="9" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="BA210" s="6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="211" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A211" s="9" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="BA211" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="212" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A212" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="BA212" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="213" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A213" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="BA213" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="214" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A214" s="9" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="BA214" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="215" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A215" s="9" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="BA215" s="6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="216" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A216" s="9" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="BA216" s="6" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="217" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A217" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="BA217" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="218" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A218" s="9" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="BA218" s="6" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="219" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A219" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="BA219" s="6" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="220" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A220" s="9" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="BA220" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="221" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A221" s="9" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="BA221" s="6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="222" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A222" s="9" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="BA222" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="223" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A223" s="9" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="BA223" s="6" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="224" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A224" s="9" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="BA224" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="225" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B225" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA225" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB225" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="226" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A226" s="10" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="BA226" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="227" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A227" s="10" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="BA227" s="6" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="228" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A228" s="10" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="BA228" s="6" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="229" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A229" s="10" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="BA229" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="230" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A230" s="10" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="BA230" s="6" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="231" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A231" s="10" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="BA231" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="232" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A232" s="10" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="BA232" s="6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="233" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A233" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="BA233" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="234" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A234" s="10" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="BA234" s="6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="235" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A235" s="10" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="BA235" s="6" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="236" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A236" s="10" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="BA236" s="6" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="237" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A237" s="10" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="BA237" s="6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="238" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A238" s="10" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="BA238" s="6" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="239" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A239" s="10" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="BA239" s="6" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="240" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A240" s="10" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="BA240" s="6" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="241" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A241" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="BA241" s="6" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="242" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A242" s="10" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="BA242" s="6" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="243" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A243" s="10" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="BA243" s="6" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="244" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A244" s="10" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="BA244" s="6" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="245" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A245" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="BA245" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="246" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A246" s="10" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="BA246" s="6" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="247" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A247" s="10" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="BA247" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="248" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A248" s="10" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="BA248" s="6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="249" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A249" s="10" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="BA249" s="6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="250" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A250" s="10" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="BA250" s="6" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="251" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A251" s="10" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="BA251" s="6" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="252" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A252" s="10" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="BA252" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="253" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A253" s="10" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="BA253" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="254" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A254" s="10" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="BA254" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="255" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A255" s="10" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="BA255" s="6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="256" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B256" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA256" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB256" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="257" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A257" s="5" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="BA257" s="6" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="258" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A258" s="5" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="BA258" s="6" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="259" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A259" s="5" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="BA259" s="6" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="260" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A260" s="5" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="BA260" s="6" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="261" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A261" s="5" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="BA261" s="6" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="262" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A262" s="5" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="BA262" s="6" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="263" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A263" s="5" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="BA263" s="6" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="264" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A264" s="5" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="BA264" s="6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="265" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A265" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="BA265" s="6" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="266" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A266" s="5" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="BA266" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="267" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A267" s="5" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="BA267" s="6" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="268" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A268" s="5" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="BA268" s="6" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="269" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A269" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="BA269" s="6" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="270" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A270" s="5" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="BA270" s="6" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="271" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A271" s="5" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="BA271" s="6" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="272" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A272" s="5" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="BA272" s="6" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="273" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A273" s="5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="BA273" s="6" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="274" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A274" s="5" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="BA274" s="6" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="275" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A275" s="5" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="BA275" s="6" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="276" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A276" s="5" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="BA276" s="6" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="277" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A277" s="5" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="BA277" s="6" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="278" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A278" s="5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="BA278" s="6" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="279" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A279" s="5" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="BA279" s="6" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="280" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A280" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="BA280" s="6" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="281" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A281" s="5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="BA281" s="6" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="282" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A282" s="5" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="BA282" s="6" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="283" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A283" s="5" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="BA283" s="6" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="284" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A284" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="BA284" s="6" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="285" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A285" s="5" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="BA285" s="6" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="286" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A286" s="5" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="BA286" s="6" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="287" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B287" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA287" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB287" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="288" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A288" s="8" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="BA288" s="6" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="289" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A289" s="8" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="BA289" s="6" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="290" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A290" s="8" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="BA290" s="6" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="291" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A291" s="8" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="BA291" s="6" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="292" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A292" s="8" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="BA292" s="6" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="293" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A293" s="8" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="BA293" s="6" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="294" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A294" s="8" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="BA294" s="6" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="295" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A295" s="8" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="BA295" s="6" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="296" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A296" s="8" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="BA296" s="6" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="297" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A297" s="8" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="BA297" s="6" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="298" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A298" s="8" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="BA298" s="6" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="299" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A299" s="8" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="BA299" s="6" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="300" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A300" s="8" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="BA300" s="6" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="301" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A301" s="8" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="BA301" s="6" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="302" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A302" s="8" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="BA302" s="6" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="303" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A303" s="8" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="BA303" s="6" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="304" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A304" s="8" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="BA304" s="6" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="305" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A305" s="8" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="BA305" s="6" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="306" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A306" s="8" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="BA306" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="307" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A307" s="8" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="BA307" s="6" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="308" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A308" s="8" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="BA308" s="6" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="309" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A309" s="8" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="BA309" s="6" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="310" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A310" s="8" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="BA310" s="6" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="311" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A311" s="8" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="BA311" s="6" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="312" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A312" s="8" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="BA312" s="6" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="313" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A313" s="8" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="BA313" s="6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="314" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A314" s="8" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="BA314" s="6" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="315" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A315" s="8" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="BA315" s="6" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="316" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A316" s="8" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="BA316" s="6" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="317" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A317" s="8" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="BA317" s="6" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="318" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B318" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA318" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB318" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="319" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A319" s="9" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="BA319" s="6" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="320" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A320" s="9" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="BA320" s="6" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="321" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A321" s="9" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="BA321" s="6" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="322" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A322" s="9" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="BA322" s="6" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="323" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A323" s="9" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="BA323" s="6" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="324" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A324" s="9" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="BA324" s="6" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="325" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A325" s="9" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="BA325" s="6" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="326" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A326" s="9" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="BA326" s="6" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="327" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A327" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="BA327" s="6" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="328" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A328" s="9" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="BA328" s="6" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="329" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A329" s="9" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="BA329" s="6" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="330" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A330" s="9" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="BA330" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="331" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A331" s="9" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="BA331" s="6" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="332" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A332" s="9" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="BA332" s="6" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="333" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A333" s="9" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="BA333" s="6" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="334" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A334" s="9" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="BA334" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="335" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A335" s="9" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="BA335" s="6" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="336" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A336" s="9" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="BA336" s="6" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="337" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A337" s="9" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="BA337" s="6" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="338" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A338" s="9" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="BA338" s="6" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="339" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A339" s="9" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="BA339" s="6" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="340" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A340" s="9" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="BA340" s="6" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="341" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A341" s="9" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="BA341" s="6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="342" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A342" s="9" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="BA342" s="6" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="343" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A343" s="9" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="BA343" s="6" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="344" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A344" s="9" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="BA344" s="6" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="345" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A345" s="9" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="BA345" s="6" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="346" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A346" s="9" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="BA346" s="6" t="s">
-        <v>653</v>
+        <v>724</v>
       </c>
     </row>
     <row r="347" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A347" s="9" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="BA347" s="6" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="348" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A348" s="9" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="BA348" s="6" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="349" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B349" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA349" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB349" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="350" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A350" s="10" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="BA350" s="6" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="351" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A351" s="10" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="BA351" s="6" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="352" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A352" s="10" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="BA352" s="6" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="353" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A353" s="10" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="BA353" s="6" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="354" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A354" s="10" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="BA354" s="6" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="355" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A355" s="10" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="BA355" s="6" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="356" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A356" s="10" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="BA356" s="6" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="357" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A357" s="10" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="BA357" s="6" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="358" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A358" s="10" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="BA358" s="6" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="359" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A359" s="10" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="BA359" s="6" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="360" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A360" s="10" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="BA360" s="6" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="361" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A361" s="10" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="BA361" s="6" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="362" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A362" s="10" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="BA362" s="6" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="363" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A363" s="10" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="BA363" s="6" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="364" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A364" s="10" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="BA364" s="6" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="365" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A365" s="10" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="BA365" s="6" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="366" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A366" s="10" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="BA366" s="6" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="367" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A367" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="BA367" s="6" t="s">
-        <v>693</v>
+        <v>723</v>
       </c>
     </row>
     <row r="368" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A368" s="10" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="BA368" s="6" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="369" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A369" s="10" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="BA369" s="6" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
     </row>
     <row r="370" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A370" s="10" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="BA370" s="6" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
     </row>
     <row r="371" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A371" s="10" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="BA371" s="6" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
     </row>
     <row r="372" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A372" s="10" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="BA372" s="6" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
     </row>
     <row r="373" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A373" s="10" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="BA373" s="6" t="s">
-        <v>705</v>
+        <v>728</v>
       </c>
     </row>
     <row r="374" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A374" s="10" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="BA374" s="6" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
     </row>
     <row r="375" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A375" s="10" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="BA375" s="6" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
     </row>
     <row r="376" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A376" s="10" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="BA376" s="6" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
     </row>
     <row r="377" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A377" s="10" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="BA377" s="6" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
     </row>
     <row r="378" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A378" s="10" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="BA378" s="6" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
     </row>
     <row r="379" spans="1:54" x14ac:dyDescent="0.4">
       <c r="A379" s="10" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="BA379" s="6" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
     </row>
     <row r="380" spans="1:54" s="7" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="B380" s="7" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="I380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="J380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="K380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="L380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="M380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="O380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="P380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Q380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="R380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="S380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="T380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="U380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="V380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="W380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="X380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Y380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="Z380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AA380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AB380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AC380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AD380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AE380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AF380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AG380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AH380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AI380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AJ380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AK380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AL380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AM380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AN380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AO380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AP380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AQ380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AR380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AS380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AT380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AU380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AV380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AW380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AX380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AY380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="AZ380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BA380" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="BB380" s="7" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
   </sheetData>
